--- a/Data/ArthurHeimCareerDataEn.xlsx
+++ b/Data/ArthurHeimCareerDataEn.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arthurheim/Library/CloudStorage/Dropbox/Travail_encrypted_decrypted/PHD/career/Data_DrivenResume/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BA54AD4-DD60-2F41-A621-536719483FC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32CF7487-A669-FA40-8BD0-3C28C505BC92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8220" yWindow="500" windowWidth="27240" windowHeight="19200" activeTab="7" xr2:uid="{65AA7443-0872-B84D-B38F-A133D7C4ED29}"/>
+    <workbookView xWindow="8220" yWindow="500" windowWidth="27240" windowHeight="19200" xr2:uid="{65AA7443-0872-B84D-B38F-A133D7C4ED29}"/>
   </bookViews>
   <sheets>
     <sheet name="education" sheetId="1" r:id="rId1"/>
@@ -18,12 +18,13 @@
     <sheet name="ScientificExpertise" sheetId="8" r:id="rId3"/>
     <sheet name="skills" sheetId="3" r:id="rId4"/>
     <sheet name="Feuil1" sheetId="7" r:id="rId5"/>
-    <sheet name="Thesis" sheetId="5" r:id="rId6"/>
-    <sheet name="Research" sheetId="9" r:id="rId7"/>
-    <sheet name="PaperDetails" sheetId="11" r:id="rId8"/>
-    <sheet name="ResearchProjects" sheetId="10" r:id="rId9"/>
-    <sheet name="conferences" sheetId="6" r:id="rId10"/>
-    <sheet name="teaching" sheetId="4" r:id="rId11"/>
+    <sheet name="Distinctions" sheetId="12" r:id="rId6"/>
+    <sheet name="Thesis" sheetId="5" r:id="rId7"/>
+    <sheet name="Research" sheetId="9" r:id="rId8"/>
+    <sheet name="PaperDetails" sheetId="11" r:id="rId9"/>
+    <sheet name="ResearchProjects" sheetId="10" r:id="rId10"/>
+    <sheet name="conferences" sheetId="6" r:id="rId11"/>
+    <sheet name="teaching" sheetId="4" r:id="rId12"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -46,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="296">
   <si>
     <t>Degree</t>
   </si>
@@ -81,13 +82,7 @@
     <t>Bachelor in Applied Economics</t>
   </si>
   <si>
-    <t>University diploma</t>
-  </si>
-  <si>
     <t>2008-2011</t>
-  </si>
-  <si>
-    <t>2008-2010</t>
   </si>
   <si>
     <t>High School diploma</t>
@@ -232,9 +227,6 @@
     <t>Major</t>
   </si>
   <si>
-    <t>Management and Economics</t>
-  </si>
-  <si>
     <t>International Economics And Development</t>
   </si>
   <si>
@@ -593,14 +585,6 @@
   </si>
   <si>
     <t xml:space="preserve">Reproducible research, integration with \LaTeX, presentations, websites </t>
-  </si>
-  <si>
-    <t>[\faAngleDoubleRight] I work in the research and statistics department of the institution in charge of all family, disability, housing and minimum income allowances in France. I use these administrative data for policy evaluations and research.
-\\ I designed and ran a randomised control trial of a welfare-to-work programme for single mothers on long term welfare.
-\\ I set-up a multi-site large scale market design experiment in a partnership with École polytechnique to assign daycare seats for local governments in France.</t>
-  </si>
-  <si>
-    <t>[\faAngleDoubleRight] I was a member of the evaluation committee of the national anti-poverty strategy and provided literature reviews, notes and proposals.</t>
   </si>
   <si>
     <t>[\faAngleDoubleRight] \underline{Master thesis}:  \emph{Public sector as a shelter ? The impact of graduating in a recession on selection into public employment.}\\
@@ -902,108 +886,125 @@
 \\ \href{https://osf.io/qhazf/}{Pre-print and replication material: \faExternalLink}</t>
   </si>
   <si>
+    <t>Policy making: building software implementing algorithms built from ISAJE at scale in France</t>
+  </si>
+  <si>
+    <t>Worked with many research teams on different aspects of the research questions. Conducted a quasi-experimental analysis of the effects of private tutoring</t>
+  </si>
+  <si>
+    <t>R \&amp; R, Nature Human Behaviour</t>
+  </si>
+  <si>
+    <t>Paris School of Economics - EHESS, ED-465, Paris I - Panthéon Sorbonne</t>
+  </si>
+  <si>
+    <t>May 2025</t>
+  </si>
+  <si>
+    <t>Association of French population economists</t>
+  </si>
+  <si>
+    <t>Marseille</t>
+  </si>
+  <si>
+    <t>Jun 2024</t>
+  </si>
+  <si>
+    <t>Conference | AFEPOP 2025</t>
+  </si>
+  <si>
+    <t>Seminar | J-pal \&amp; IPP</t>
+  </si>
+  <si>
+    <t>Seminar | Public economics</t>
+  </si>
+  <si>
+    <t>OECD expert group |  ‘What standards of evidence are needed for policy design, implementation and evaluation’</t>
+  </si>
+  <si>
+    <t>\emph{Demand for international standards of evidence : thoughts from a French perspective}</t>
+  </si>
+  <si>
+    <t>International conference | Using educational research and innovation to address inequality and achievement gaps in education</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> \emph{Income support strategies to reduce inequalities : Insights from France}</t>
+  </si>
+  <si>
+    <t>Conference | Social investment for the youths</t>
+  </si>
+  <si>
+    <t>Seminar | education policies</t>
+  </si>
+  <si>
+    <t>Conference | Evaluating public policies</t>
+  </si>
+  <si>
+    <t>AFSE \&amp; DG Trésor</t>
+  </si>
+  <si>
+    <t>Strasbourg</t>
+  </si>
+  <si>
+    <t>Training futur high-level civil servants to public policy evaluation and anti-poverty policies</t>
+  </si>
+  <si>
+    <t>Institut national des études teritoriales (INET)</t>
+  </si>
+  <si>
+    <t>École nationale supérieure de la sécurité sociale (EN3S)</t>
+  </si>
+  <si>
+    <t>Institut de la gestion publique et du développement économique (IGPDE)</t>
+  </si>
+  <si>
+    <t>Participating in the evaluation of the effects of the national strategy to prevent and combat poverty, chaired by Louis Schweitzer.</t>
+  </si>
+  <si>
+    <t>Propose public policy initiatives focusing on the development, fulfilment and acquisition of young children.</t>
+  </si>
+  <si>
+    <t>Nature Human Behaviour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{\bf Forthcoming} </t>
+  </si>
+  <si>
+    <t>{\bf R \&amp; R} Nature Human Behaviour</t>
+  </si>
+  <si>
+    <t>Working paper</t>
+  </si>
+  <si>
+    <t>A randomised controlled trial on the effect of administrative burden and information costs on social inequalities in early childcare access in France</t>
+  </si>
+  <si>
+    <t>Cour des comptes</t>
+  </si>
+  <si>
+    <t>Handed down by the First President of the Court on May 27, 2025</t>
+  </si>
+  <si>
+    <t>[\faAngleDoubleRight] I work in the research and statistics department of the institution in charge of all family, disability, housing and minimum income allowances in France. I use these administrative data for policy evaluations and research.</t>
+  </si>
+  <si>
+    <t>\href{https://www.ccomptes.fr/fr/actualites/la-cour-des-comptes-decerne-son-prix-de-these-2025}{Best PhD dissertation award}</t>
+  </si>
+  <si>
+    <t>1st prize (ex-æquo)</t>
+  </si>
+  <si>
     <t xml:space="preserve">[\faAngleDoubleRight] \underline{PhD thesis}: \emph{\href{https://hal.science/tel-04801852v1}{Social investment and the changing face of poverty: Essays on the design and evaluation of social and family policies in France}} \\
  \underline{PhD advisor:} \href{https://www.parisschoolofeconomics.eu/en/gurgand-marc/}{Marc Gurgand}  \\
  \underline{ Jury}:  \href{http://www.anneboring.com/}{Anne Boring}, \href{https://sites.google.com/site/rafaellalive/}{Rafael Lalive}, \href{https://sites.google.com/view/camilleterrier/accueil}{Camille Terrier}, \href{https://www.parisschoolofeconomics.eu/en/macours-karen/}{Karen Macours} \\
-\href{https://theses.fr/2024EHES0027}{Online access: \faExternalLink} 
-\\ \href{https://www.dropbox.com/scl/fi/7yl7ri3en9vak8h2nyt44/R-sum-AHeimPhDV2.pdf?rlkey=w9k81hwyt6eu6390tgd1mqa6u&amp;dl=0}{Summary in French: \faExternalLink} </t>
-  </si>
-  <si>
-    <t>Policy making: building software implementing algorithms built from ISAJE at scale in France</t>
-  </si>
-  <si>
-    <t>Worked with many research teams on different aspects of the research questions. Conducted a quasi-experimental analysis of the effects of private tutoring</t>
-  </si>
-  <si>
-    <t>R \&amp; R, Nature Human Behaviour</t>
-  </si>
-  <si>
-    <t>Paris School of Economics - EHESS, ED-465, Paris I - Panthéon Sorbonne</t>
-  </si>
-  <si>
-    <t>May 2025</t>
-  </si>
-  <si>
-    <t>Association of French population economists</t>
-  </si>
-  <si>
-    <t>Marseille</t>
-  </si>
-  <si>
-    <t>Jun 2024</t>
-  </si>
-  <si>
-    <t>Conference | AFEPOP 2025</t>
-  </si>
-  <si>
-    <t>Seminar | J-pal \&amp; IPP</t>
-  </si>
-  <si>
-    <t>Seminar | Public economics</t>
-  </si>
-  <si>
-    <t>OECD expert group |  ‘What standards of evidence are needed for policy design, implementation and evaluation’</t>
-  </si>
-  <si>
-    <t>\emph{Demand for international standards of evidence : thoughts from a French perspective}</t>
-  </si>
-  <si>
-    <t>International conference | Using educational research and innovation to address inequality and achievement gaps in education</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> \emph{Income support strategies to reduce inequalities : Insights from France}</t>
-  </si>
-  <si>
-    <t>Conference | Social investment for the youths</t>
-  </si>
-  <si>
-    <t>Seminar | education policies</t>
-  </si>
-  <si>
-    <t>Conference | Evaluating public policies</t>
-  </si>
-  <si>
-    <t>AFSE \&amp; DG Trésor</t>
-  </si>
-  <si>
-    <t>Strasbourg</t>
-  </si>
-  <si>
-    <t>Training futur high-level civil servants to public policy evaluation and anti-poverty policies</t>
-  </si>
-  <si>
-    <t>Institut national des études teritoriales (INET)</t>
-  </si>
-  <si>
-    <t>École nationale supérieure de la sécurité sociale (EN3S)</t>
-  </si>
-  <si>
-    <t>Institut de la gestion publique et du développement économique (IGPDE)</t>
-  </si>
-  <si>
-    <t>Participating in the evaluation of the effects of the national strategy to prevent and combat poverty, chaired by Louis Schweitzer.</t>
-  </si>
-  <si>
-    <t>Propose public policy initiatives focusing on the development, fulfilment and acquisition of young children.</t>
-  </si>
-  <si>
-    <t>Nature Human Behaviour</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{\bf Forthcoming} </t>
-  </si>
-  <si>
-    <t>{\bf R \&amp; R} Nature Human Behaviour</t>
-  </si>
-  <si>
-    <t>{\bf R \&amp; R} European Economic Review</t>
+\href{https://theses.fr/2024EHES0027}{Online access: \faExternalLink}  $\quad$ \href{https://www.dropbox.com/scl/fi/7yl7ri3en9vak8h2nyt44/R-sum-AHeimPhDV2.pdf?rlkey=w9k81hwyt6eu6390tgd1mqa6u&amp;dl=0}{Summary in French: \faExternalLink} </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14">
+  <fonts count="16">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1023,11 +1024,6 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="CMR10"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="CMBX10"/>
     </font>
     <font>
       <b/>
@@ -1099,6 +1095,23 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="CMR10"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="CMBX10"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1119,9 +1132,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1129,46 +1142,52 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="16" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="16" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -1504,7 +1523,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F464DC6A-27D2-7946-9BDF-A29EA65BBB42}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="3" max="3" width="23.5" customWidth="1"/>
@@ -1513,19 +1532,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E1" s="4" t="s">
+      <c r="D1" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1537,13 +1556,13 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="D2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>264</v>
+        <v>295</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="34">
@@ -1554,13 +1573,13 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1568,41 +1587,27 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
         <v>7</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5">
+        <v>2007</v>
+      </c>
+      <c r="C5" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" t="s">
-        <v>7</v>
-      </c>
       <c r="D5" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6">
-        <v>2007</v>
-      </c>
-      <c r="C6" t="s">
-        <v>61</v>
-      </c>
-      <c r="D6" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -1611,6 +1616,254 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11C59C71-C1DE-6345-8FA1-424DE87D1118}">
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <cols>
+    <col min="5" max="5" width="26.5" customWidth="1"/>
+    <col min="6" max="6" width="53.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>209</v>
+      </c>
+      <c r="B2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C2" t="s">
+        <v>199</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="E2" s="26" t="s">
+        <v>244</v>
+      </c>
+      <c r="F2" t="s">
+        <v>204</v>
+      </c>
+      <c r="G2" t="s">
+        <v>211</v>
+      </c>
+      <c r="H2" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C3" t="s">
+        <v>200</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="E3" s="26" t="s">
+        <v>244</v>
+      </c>
+      <c r="F3" t="s">
+        <v>203</v>
+      </c>
+      <c r="G3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>213</v>
+      </c>
+      <c r="B4" t="s">
+        <v>216</v>
+      </c>
+      <c r="C4" t="s">
+        <v>201</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="E4" s="26" t="s">
+        <v>245</v>
+      </c>
+      <c r="F4" t="s">
+        <v>205</v>
+      </c>
+      <c r="G4" t="s">
+        <v>211</v>
+      </c>
+      <c r="H4" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>214</v>
+      </c>
+      <c r="B5" t="s">
+        <v>216</v>
+      </c>
+      <c r="C5" t="s">
+        <v>201</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="E5" s="26" t="s">
+        <v>246</v>
+      </c>
+      <c r="F5" t="s">
+        <v>206</v>
+      </c>
+      <c r="G5" t="s">
+        <v>210</v>
+      </c>
+      <c r="H5" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>218</v>
+      </c>
+      <c r="B6" t="s">
+        <v>216</v>
+      </c>
+      <c r="C6" t="s">
+        <v>202</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="E6" s="26" t="s">
+        <v>246</v>
+      </c>
+      <c r="F6" t="s">
+        <v>259</v>
+      </c>
+      <c r="G6" t="s">
+        <v>210</v>
+      </c>
+      <c r="H6" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>215</v>
+      </c>
+      <c r="B7" t="s">
+        <v>216</v>
+      </c>
+      <c r="C7" t="s">
+        <v>202</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="E7" s="26" t="s">
+        <v>246</v>
+      </c>
+      <c r="F7" t="s">
+        <v>207</v>
+      </c>
+      <c r="G7" t="s">
+        <v>210</v>
+      </c>
+      <c r="H7" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>252</v>
+      </c>
+      <c r="B8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" t="s">
+        <v>253</v>
+      </c>
+      <c r="D8">
+        <v>2013</v>
+      </c>
+      <c r="E8">
+        <v>2014</v>
+      </c>
+      <c r="F8" t="s">
+        <v>254</v>
+      </c>
+      <c r="G8" t="s">
+        <v>211</v>
+      </c>
+      <c r="H8" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>255</v>
+      </c>
+      <c r="B9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" t="s">
+        <v>202</v>
+      </c>
+      <c r="D9">
+        <v>2014</v>
+      </c>
+      <c r="E9">
+        <v>2016</v>
+      </c>
+      <c r="F9" t="s">
+        <v>260</v>
+      </c>
+      <c r="G9" t="s">
+        <v>211</v>
+      </c>
+      <c r="H9" t="s">
+        <v>256</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89004A4C-135E-AE46-AB58-A9B77E14C3A4}">
   <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
@@ -1619,245 +1872,245 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="G1" s="5"/>
+      <c r="D1" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" s="4"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="B2" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="C2" t="s">
-        <v>271</v>
-      </c>
-      <c r="D2" s="29" t="s">
-        <v>269</v>
+        <v>265</v>
+      </c>
+      <c r="D2" s="28" t="s">
+        <v>263</v>
       </c>
       <c r="E2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G2" s="5"/>
+        <v>21</v>
+      </c>
+      <c r="G2" s="4"/>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>195</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="D3" s="28" t="s">
-        <v>199</v>
+        <v>190</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="D3" s="27" t="s">
+        <v>194</v>
       </c>
       <c r="E3" t="s">
-        <v>116</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>23</v>
+        <v>113</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C4" t="s">
-        <v>107</v>
-      </c>
-      <c r="D4" s="27" t="s">
-        <v>272</v>
+        <v>104</v>
+      </c>
+      <c r="D4" s="26" t="s">
+        <v>266</v>
       </c>
       <c r="E4" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="F4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B5" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C5" t="s">
-        <v>107</v>
-      </c>
-      <c r="D5" s="27" t="s">
-        <v>124</v>
+        <v>104</v>
+      </c>
+      <c r="D5" s="26" t="s">
+        <v>121</v>
       </c>
       <c r="E5" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="B6" t="s">
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>107</v>
-      </c>
-      <c r="D6" s="27" t="s">
-        <v>123</v>
+        <v>104</v>
+      </c>
+      <c r="D6" s="26" t="s">
+        <v>120</v>
       </c>
       <c r="E6" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="B7" t="s">
+        <v>111</v>
+      </c>
+      <c r="C7" t="s">
+        <v>104</v>
+      </c>
+      <c r="D7" s="26" t="s">
+        <v>119</v>
+      </c>
+      <c r="E7" t="s">
         <v>114</v>
       </c>
-      <c r="C7" t="s">
-        <v>107</v>
-      </c>
-      <c r="D7" s="27" t="s">
-        <v>122</v>
-      </c>
-      <c r="E7" t="s">
-        <v>117</v>
-      </c>
       <c r="F7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="B8" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C8" t="s">
-        <v>107</v>
-      </c>
-      <c r="D8" s="27" t="s">
-        <v>121</v>
+        <v>104</v>
+      </c>
+      <c r="D8" s="26" t="s">
+        <v>118</v>
       </c>
       <c r="E8" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="F8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="B9" t="s">
+        <v>107</v>
+      </c>
+      <c r="C9" t="s">
         <v>110</v>
       </c>
-      <c r="C9" t="s">
-        <v>113</v>
-      </c>
-      <c r="D9" s="27" t="s">
-        <v>120</v>
+      <c r="D9" s="26" t="s">
+        <v>117</v>
       </c>
       <c r="E9" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="F9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="B10" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="C10" t="s">
-        <v>107</v>
-      </c>
-      <c r="D10" s="27" t="s">
-        <v>120</v>
+        <v>104</v>
+      </c>
+      <c r="D10" s="26" t="s">
+        <v>117</v>
       </c>
       <c r="E10" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="B11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C11" t="s">
-        <v>107</v>
-      </c>
-      <c r="D11" s="27" t="s">
-        <v>119</v>
+        <v>104</v>
+      </c>
+      <c r="D11" s="26" t="s">
+        <v>116</v>
       </c>
       <c r="E11" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="B12" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C12" t="s">
-        <v>107</v>
-      </c>
-      <c r="D12" s="29" t="s">
-        <v>118</v>
+        <v>104</v>
+      </c>
+      <c r="D12" s="28" t="s">
+        <v>115</v>
       </c>
       <c r="E12" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F12" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -1868,113 +2121,113 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A382872-5565-5645-A6BC-BA5C4FC5CD7B}">
   <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="D1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="E1" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="F1" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>20</v>
-      </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="E2" s="18" t="s">
         <v>154</v>
       </c>
-      <c r="B2" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="C2" s="18" t="s">
-        <v>155</v>
-      </c>
-      <c r="D2" s="18" t="s">
-        <v>156</v>
-      </c>
-      <c r="E2" s="19" t="s">
-        <v>157</v>
-      </c>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18" t="s">
-        <v>194</v>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B3" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>83</v>
+        <v>76</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>80</v>
       </c>
       <c r="E3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G3" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B4" t="s">
         <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E4" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="G4" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B5" t="s">
         <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D5" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E5" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="G5" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -1997,163 +2250,161 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="G1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="H1" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="51">
+      <c r="A2" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="E2" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="F2" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="G2" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="H1" s="5" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="119">
-      <c r="A2" s="7" t="s">
+      <c r="H2" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" s="8"/>
+      <c r="G3" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="C2" s="7" t="s">
+      <c r="B4" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" s="8"/>
+      <c r="G4" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="D2" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F2" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="G2" s="7" t="s">
+      <c r="E5" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="8"/>
+      <c r="G5" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5" t="s">
         <v>23</v>
       </c>
-      <c r="H2" s="7" t="s">
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F6" s="8"/>
+      <c r="G6" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H6" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="F4" s="9"/>
-      <c r="G4" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" s="9"/>
-      <c r="G5" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F6" s="9"/>
-      <c r="G6" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H6" t="s">
-        <v>25</v>
-      </c>
-    </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="7"/>
+      <c r="A7" s="6"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2166,184 +2417,184 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="G1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F1" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>62</v>
+      <c r="H1" s="4" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>191</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="D2" s="5">
+        <v>186</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="D2" s="4">
         <v>2025</v>
       </c>
-      <c r="E2" s="30" t="s">
-        <v>157</v>
+      <c r="E2" s="29" t="s">
+        <v>154</v>
       </c>
       <c r="F2" t="s">
-        <v>285</v>
-      </c>
-      <c r="G2" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2" s="4" t="s">
         <v>23</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>186</v>
-      </c>
-      <c r="B3" s="14" t="s">
-        <v>187</v>
+        <v>181</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>182</v>
       </c>
       <c r="C3" t="s">
-        <v>188</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>244</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>245</v>
+        <v>183</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>240</v>
       </c>
       <c r="F3" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="G3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" t="s">
         <v>23</v>
-      </c>
-      <c r="H3" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="B4" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="C4" t="s">
-        <v>105</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>246</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>245</v>
+        <v>102</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>240</v>
       </c>
       <c r="F4" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="G4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" t="s">
         <v>23</v>
-      </c>
-      <c r="H4" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="B5" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="C5" t="s">
-        <v>107</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>247</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>157</v>
+        <v>104</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>154</v>
       </c>
       <c r="F5" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="G5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5" t="s">
         <v>23</v>
-      </c>
-      <c r="H5" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="B6" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="C6" t="s">
-        <v>107</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>247</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>247</v>
+        <v>104</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>242</v>
       </c>
       <c r="F6" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="G6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H6" t="s">
         <v>23</v>
       </c>
-      <c r="H6" t="s">
-        <v>25</v>
-      </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="20"/>
+      <c r="A7" s="19"/>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="20"/>
+      <c r="A10" s="19"/>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="10"/>
+      <c r="A12" s="9"/>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="20"/>
+      <c r="A13" s="19"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="10"/>
+      <c r="A15" s="9"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="20"/>
+      <c r="A16" s="19"/>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="10"/>
+      <c r="A18" s="9"/>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="20"/>
+      <c r="A19" s="19"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2361,90 +2612,90 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C1" t="s">
         <v>161</v>
-      </c>
-      <c r="B1" t="s">
-        <v>162</v>
-      </c>
-      <c r="C1" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B2" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C2" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="B3" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B4" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C4" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
+        <v>162</v>
+      </c>
+      <c r="B5" t="s">
+        <v>163</v>
+      </c>
+      <c r="C5" t="s">
         <v>165</v>
-      </c>
-      <c r="B5" t="s">
-        <v>166</v>
-      </c>
-      <c r="C5" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="B6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C6" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B7" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C7" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B8" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C8" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -2459,189 +2710,189 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>135</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>145</v>
+        <v>132</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B5" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C5" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C6" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C7" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C8" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B9" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C9" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B10" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C10" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B11" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C11" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B12" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C12" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C13" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B14" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C14" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B15" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C15" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B16" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C16" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B17" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C17" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -2650,6 +2901,71 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CB17877-D33C-1E40-9453-E2225190AABA}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1" s="30" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="119">
+      <c r="A2" s="31" t="s">
+        <v>293</v>
+      </c>
+      <c r="B2" s="31">
+        <v>2025</v>
+      </c>
+      <c r="C2" s="31" t="s">
+        <v>290</v>
+      </c>
+      <c r="D2" s="31" t="s">
+        <v>294</v>
+      </c>
+      <c r="E2" s="32" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="31"/>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="32"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="31"/>
+      <c r="B4" s="31"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="31"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="34"/>
+      <c r="B5" s="31"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="31"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{384B73DB-6D0E-814C-974E-66FDADDCAF85}">
   <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="24" customHeight="1"/>
@@ -2665,220 +2981,220 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="24" customHeight="1">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>77</v>
+      <c r="E1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="24" customHeight="1">
       <c r="A2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E2">
         <v>2024</v>
       </c>
       <c r="F2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="G2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H2" s="17" t="s">
-        <v>183</v>
+        <v>21</v>
+      </c>
+      <c r="H2" s="16" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="24" customHeight="1">
       <c r="A3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E3">
         <v>2024</v>
       </c>
       <c r="F3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H3" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="24" customHeight="1">
       <c r="A4" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E4">
         <v>2024</v>
       </c>
       <c r="F4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H4" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="24" customHeight="1">
       <c r="A5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" t="s">
         <v>50</v>
       </c>
-      <c r="C5" t="s">
-        <v>52</v>
-      </c>
       <c r="D5" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E5">
         <v>2024</v>
       </c>
       <c r="F5" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="G5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H5" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="24" customHeight="1">
       <c r="A6" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D6" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="E6">
         <v>2024</v>
       </c>
       <c r="F6" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="G6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="24" customHeight="1">
       <c r="A7" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C7" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E7" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F7" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="24" customHeight="1">
       <c r="A8" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B8" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D8" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E8">
         <v>2026</v>
       </c>
       <c r="F8" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="24" customHeight="1">
-      <c r="B9" s="16" t="s">
-        <v>126</v>
+      <c r="B9" s="15" t="s">
+        <v>123</v>
       </c>
       <c r="C9" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D9" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E9">
         <v>2024</v>
       </c>
       <c r="F9" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="24" customHeight="1">
-      <c r="B10" s="15"/>
+      <c r="B10" s="14"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -2888,229 +3204,229 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79EF90B3-AE5D-E640-BB84-BA742FCD421F}">
   <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="33.83203125" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="16384" width="33.83203125" style="23"/>
+    <col min="1" max="16384" width="33.83203125" style="22"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="17">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="D1" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="C1" s="21" t="s">
+      <c r="E1" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="H1" s="20" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="85">
+      <c r="A2" s="23"/>
+      <c r="B2" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23" t="s">
+        <v>197</v>
+      </c>
+      <c r="E2" s="23">
+        <v>2024</v>
+      </c>
+      <c r="F2" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="G2" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2" s="24" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="85">
+      <c r="A3" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="D3" s="23" t="s">
         <v>66</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="E3" s="23">
+        <v>2024</v>
+      </c>
+      <c r="F3" s="23" t="s">
+        <v>195</v>
+      </c>
+      <c r="G3" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="23" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="119">
+      <c r="A4" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" s="23"/>
+      <c r="D4" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="E4" s="23">
+        <v>2024</v>
+      </c>
+      <c r="F4" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="G4" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" s="23" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="221">
+      <c r="A5" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="D5" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="E5" s="23">
+        <v>2024</v>
+      </c>
+      <c r="F5" s="23" t="s">
+        <v>198</v>
+      </c>
+      <c r="G5" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5" s="23" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="221">
+      <c r="A6" s="23"/>
+      <c r="B6" s="23" t="s">
+        <v>196</v>
+      </c>
+      <c r="C6" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="E1" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="F1" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="G1" s="21" t="s">
-        <v>76</v>
-      </c>
-      <c r="H1" s="21" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="85">
-      <c r="A2" s="24"/>
-      <c r="B2" s="24" t="s">
-        <v>53</v>
-      </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24" t="s">
-        <v>202</v>
-      </c>
-      <c r="E2" s="24">
+      <c r="D6" s="23" t="s">
+        <v>261</v>
+      </c>
+      <c r="E6" s="23">
         <v>2024</v>
       </c>
-      <c r="F2" s="24" t="s">
-        <v>73</v>
-      </c>
-      <c r="G2" s="24" t="s">
+      <c r="F6" s="23" t="s">
+        <v>90</v>
+      </c>
+      <c r="G6" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="H6" s="23"/>
+    </row>
+    <row r="7" spans="1:8" ht="102">
+      <c r="A7" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="B7" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="D7" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="E7" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F7" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="G7" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="H2" s="25" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="85">
-      <c r="A3" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="B3" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="C3" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="D3" s="24" t="s">
-        <v>69</v>
-      </c>
-      <c r="E3" s="24">
+      <c r="H7" s="23"/>
+    </row>
+    <row r="8" spans="1:8" ht="119">
+      <c r="A8" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="B8" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="C8" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="E8" s="23">
+        <v>2026</v>
+      </c>
+      <c r="F8" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="G8" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" s="23"/>
+    </row>
+    <row r="9" spans="1:8" ht="153">
+      <c r="A9" s="23"/>
+      <c r="B9" s="25" t="s">
+        <v>123</v>
+      </c>
+      <c r="C9" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="D9" s="23" t="s">
+        <v>261</v>
+      </c>
+      <c r="E9" s="23">
         <v>2024</v>
       </c>
-      <c r="F3" s="24" t="s">
-        <v>200</v>
-      </c>
-      <c r="G3" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="H3" s="24" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="119">
-      <c r="A4" s="24" t="s">
-        <v>63</v>
-      </c>
-      <c r="B4" s="24" t="s">
-        <v>49</v>
-      </c>
-      <c r="C4" s="24"/>
-      <c r="D4" s="24" t="s">
-        <v>69</v>
-      </c>
-      <c r="E4" s="24">
-        <v>2024</v>
-      </c>
-      <c r="F4" s="24" t="s">
-        <v>55</v>
-      </c>
-      <c r="G4" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="H4" s="24" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="221">
-      <c r="A5" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="B5" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="C5" s="24" t="s">
-        <v>52</v>
-      </c>
-      <c r="D5" s="24" t="s">
-        <v>69</v>
-      </c>
-      <c r="E5" s="24">
-        <v>2024</v>
-      </c>
-      <c r="F5" s="24" t="s">
-        <v>203</v>
-      </c>
-      <c r="G5" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="H5" s="24" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="221">
-      <c r="A6" s="24"/>
-      <c r="B6" s="24" t="s">
-        <v>201</v>
-      </c>
-      <c r="C6" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="D6" s="24" t="s">
-        <v>267</v>
-      </c>
-      <c r="E6" s="24">
-        <v>2024</v>
-      </c>
-      <c r="F6" s="24" t="s">
-        <v>93</v>
-      </c>
-      <c r="G6" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="H6" s="24"/>
-    </row>
-    <row r="7" spans="1:8" ht="102">
-      <c r="A7" s="24" t="s">
-        <v>63</v>
-      </c>
-      <c r="B7" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="C7" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="D7" s="24" t="s">
-        <v>74</v>
-      </c>
-      <c r="E7" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="F7" s="24" t="s">
-        <v>96</v>
-      </c>
-      <c r="G7" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="H7" s="24"/>
-    </row>
-    <row r="8" spans="1:8" ht="119">
-      <c r="A8" s="24" t="s">
-        <v>97</v>
-      </c>
-      <c r="B8" s="24" t="s">
-        <v>103</v>
-      </c>
-      <c r="C8" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="D8" s="24" t="s">
-        <v>74</v>
-      </c>
-      <c r="E8" s="24">
-        <v>2026</v>
-      </c>
-      <c r="F8" s="24" t="s">
-        <v>98</v>
-      </c>
-      <c r="G8" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="H8" s="24"/>
-    </row>
-    <row r="9" spans="1:8" ht="153">
-      <c r="A9" s="24"/>
-      <c r="B9" s="26" t="s">
-        <v>126</v>
-      </c>
-      <c r="C9" s="24" t="s">
-        <v>128</v>
-      </c>
-      <c r="D9" s="24" t="s">
-        <v>267</v>
-      </c>
-      <c r="E9" s="24">
-        <v>2024</v>
-      </c>
-      <c r="F9" s="24" t="s">
-        <v>127</v>
-      </c>
-      <c r="G9" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="H9" s="24"/>
+      <c r="F9" s="23" t="s">
+        <v>124</v>
+      </c>
+      <c r="G9" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="H9" s="23"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -3120,247 +3436,247 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9C8C5BE-4484-E84F-BDDE-C414E19C95A4}">
   <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="31.6640625" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="1:9" ht="17">
-      <c r="A1" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="B1" s="21" t="s">
+      <c r="A1" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="C1" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="D1" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="E1" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="F1" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="G1" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="H1" s="21" t="s">
-        <v>76</v>
-      </c>
-      <c r="I1" s="21" t="s">
-        <v>77</v>
+      <c r="F1" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="I1" s="20" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="136">
       <c r="A2" t="s">
-        <v>228</v>
-      </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24" t="s">
-        <v>53</v>
-      </c>
-      <c r="D2" s="24" t="s">
-        <v>243</v>
-      </c>
-      <c r="E2" s="24" t="s">
-        <v>202</v>
-      </c>
-      <c r="F2" s="24">
+        <v>223</v>
+      </c>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" s="23" t="s">
+        <v>238</v>
+      </c>
+      <c r="E2" s="23" t="s">
+        <v>197</v>
+      </c>
+      <c r="F2" s="23">
         <v>2024</v>
       </c>
-      <c r="G2" s="24" t="s">
-        <v>241</v>
-      </c>
-      <c r="H2" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="I2" s="25" t="s">
-        <v>183</v>
+      <c r="G2" s="23" t="s">
+        <v>236</v>
+      </c>
+      <c r="H2" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" s="24" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="289">
       <c r="A3" t="s">
+        <v>224</v>
+      </c>
+      <c r="B3" s="23"/>
+      <c r="C3" s="23" t="s">
+        <v>228</v>
+      </c>
+      <c r="D3" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="E3" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="F3" s="23">
+        <v>2024</v>
+      </c>
+      <c r="G3" s="23" t="s">
+        <v>232</v>
+      </c>
+      <c r="H3" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="23" t="s">
         <v>229</v>
-      </c>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24" t="s">
-        <v>233</v>
-      </c>
-      <c r="D3" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="E3" s="24" t="s">
-        <v>69</v>
-      </c>
-      <c r="F3" s="24">
-        <v>2024</v>
-      </c>
-      <c r="G3" s="24" t="s">
-        <v>237</v>
-      </c>
-      <c r="H3" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="I3" s="24" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="119">
       <c r="A4" t="s">
+        <v>225</v>
+      </c>
+      <c r="B4" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4" s="23" t="s">
         <v>230</v>
       </c>
-      <c r="B4" s="24" t="s">
-        <v>63</v>
-      </c>
-      <c r="C4" s="24" t="s">
-        <v>235</v>
-      </c>
-      <c r="D4" s="24" t="s">
-        <v>243</v>
-      </c>
-      <c r="E4" s="24" t="s">
-        <v>294</v>
-      </c>
-      <c r="F4" s="24">
+      <c r="D4" s="23" t="s">
+        <v>238</v>
+      </c>
+      <c r="E4" s="23" t="s">
+        <v>288</v>
+      </c>
+      <c r="F4" s="23">
         <v>2024</v>
       </c>
-      <c r="G4" s="24" t="s">
-        <v>263</v>
-      </c>
-      <c r="H4" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="I4" s="24" t="s">
-        <v>130</v>
+      <c r="G4" s="23" t="s">
+        <v>258</v>
+      </c>
+      <c r="H4" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" s="23" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="306">
       <c r="A5" t="s">
+        <v>226</v>
+      </c>
+      <c r="B5" s="23"/>
+      <c r="C5" s="23" t="s">
         <v>231</v>
       </c>
-      <c r="B5" s="24"/>
-      <c r="C5" s="24" t="s">
-        <v>236</v>
-      </c>
-      <c r="D5" s="24" t="s">
-        <v>52</v>
-      </c>
-      <c r="E5" s="24" t="s">
-        <v>69</v>
-      </c>
-      <c r="F5" s="24">
+      <c r="D5" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="E5" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="F5" s="23">
         <v>2024</v>
       </c>
-      <c r="G5" s="24" t="s">
-        <v>239</v>
-      </c>
-      <c r="H5" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="I5" s="24" t="s">
-        <v>131</v>
+      <c r="G5" s="23" t="s">
+        <v>234</v>
+      </c>
+      <c r="H5" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" s="23" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="170">
       <c r="A6" t="s">
-        <v>232</v>
-      </c>
-      <c r="B6" s="24"/>
-      <c r="C6" s="24" t="s">
-        <v>201</v>
-      </c>
-      <c r="D6" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="E6" s="24" t="s">
-        <v>291</v>
-      </c>
-      <c r="F6" s="24" t="s">
-        <v>292</v>
-      </c>
-      <c r="G6" s="24" t="s">
-        <v>238</v>
-      </c>
-      <c r="H6" s="24" t="s">
+        <v>227</v>
+      </c>
+      <c r="B6" s="23"/>
+      <c r="C6" s="23" t="s">
+        <v>289</v>
+      </c>
+      <c r="D6" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="E6" s="23" t="s">
+        <v>285</v>
+      </c>
+      <c r="F6" s="23" t="s">
+        <v>286</v>
+      </c>
+      <c r="G6" s="23" t="s">
+        <v>233</v>
+      </c>
+      <c r="H6" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" s="23"/>
+    </row>
+    <row r="7" spans="1:9" ht="119">
+      <c r="B7" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="D7" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="E7" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="F7" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="G7" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="H7" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="I6" s="24"/>
-    </row>
-    <row r="7" spans="1:9" ht="119">
-      <c r="B7" s="24" t="s">
-        <v>63</v>
-      </c>
-      <c r="C7" s="24" t="s">
+      <c r="I7" s="23"/>
+    </row>
+    <row r="8" spans="1:9" ht="119">
+      <c r="B8" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="D7" s="24" t="s">
+      <c r="C8" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="D8" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="F8" s="23">
+        <v>2026</v>
+      </c>
+      <c r="G8" s="23" t="s">
         <v>95</v>
       </c>
-      <c r="E7" s="24" t="s">
-        <v>74</v>
-      </c>
-      <c r="F7" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="G7" s="24" t="s">
-        <v>96</v>
-      </c>
-      <c r="H7" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="I7" s="24"/>
-    </row>
-    <row r="8" spans="1:9" ht="119">
-      <c r="B8" s="24" t="s">
-        <v>97</v>
-      </c>
-      <c r="C8" s="24" t="s">
-        <v>103</v>
-      </c>
-      <c r="D8" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="E8" s="24" t="s">
-        <v>74</v>
-      </c>
-      <c r="F8" s="24">
-        <v>2026</v>
-      </c>
-      <c r="G8" s="24" t="s">
-        <v>98</v>
-      </c>
-      <c r="H8" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="I8" s="24"/>
+      <c r="H8" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="I8" s="23"/>
     </row>
     <row r="9" spans="1:9" ht="85">
       <c r="A9" t="s">
-        <v>240</v>
-      </c>
-      <c r="B9" s="24"/>
-      <c r="C9" s="26" t="s">
-        <v>126</v>
-      </c>
-      <c r="D9" s="24" t="s">
-        <v>128</v>
-      </c>
-      <c r="E9" s="24" t="s">
-        <v>293</v>
-      </c>
-      <c r="F9" s="24">
+        <v>235</v>
+      </c>
+      <c r="B9" s="23"/>
+      <c r="C9" s="25" t="s">
+        <v>123</v>
+      </c>
+      <c r="D9" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="E9" s="23" t="s">
+        <v>287</v>
+      </c>
+      <c r="F9" s="23">
         <v>2024</v>
       </c>
-      <c r="G9" s="24" t="s">
-        <v>242</v>
-      </c>
-      <c r="H9" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="I9" s="24"/>
+      <c r="G9" s="23" t="s">
+        <v>237</v>
+      </c>
+      <c r="H9" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="I9" s="23"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -3368,252 +3684,4 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11C59C71-C1DE-6345-8FA1-424DE87D1118}">
-  <dimension ref="A1:H9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
-  <cols>
-    <col min="5" max="5" width="26.5" customWidth="1"/>
-    <col min="6" max="6" width="53.5" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" t="s">
-        <v>214</v>
-      </c>
-      <c r="B2" t="s">
-        <v>221</v>
-      </c>
-      <c r="C2" t="s">
-        <v>204</v>
-      </c>
-      <c r="D2" s="13" t="s">
-        <v>248</v>
-      </c>
-      <c r="E2" s="27" t="s">
-        <v>249</v>
-      </c>
-      <c r="F2" t="s">
-        <v>209</v>
-      </c>
-      <c r="G2" t="s">
-        <v>216</v>
-      </c>
-      <c r="H2" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" t="s">
-        <v>217</v>
-      </c>
-      <c r="B3" t="s">
-        <v>222</v>
-      </c>
-      <c r="C3" t="s">
-        <v>205</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>245</v>
-      </c>
-      <c r="E3" s="27" t="s">
-        <v>249</v>
-      </c>
-      <c r="F3" t="s">
-        <v>208</v>
-      </c>
-      <c r="G3" t="s">
-        <v>216</v>
-      </c>
-      <c r="H3" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" t="s">
-        <v>218</v>
-      </c>
-      <c r="B4" t="s">
-        <v>221</v>
-      </c>
-      <c r="C4" t="s">
-        <v>206</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>244</v>
-      </c>
-      <c r="E4" s="27" t="s">
-        <v>250</v>
-      </c>
-      <c r="F4" t="s">
-        <v>210</v>
-      </c>
-      <c r="G4" t="s">
-        <v>216</v>
-      </c>
-      <c r="H4" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" t="s">
-        <v>219</v>
-      </c>
-      <c r="B5" t="s">
-        <v>221</v>
-      </c>
-      <c r="C5" t="s">
-        <v>206</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>244</v>
-      </c>
-      <c r="E5" s="27" t="s">
-        <v>251</v>
-      </c>
-      <c r="F5" t="s">
-        <v>211</v>
-      </c>
-      <c r="G5" t="s">
-        <v>215</v>
-      </c>
-      <c r="H5" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" t="s">
-        <v>223</v>
-      </c>
-      <c r="B6" t="s">
-        <v>221</v>
-      </c>
-      <c r="C6" t="s">
-        <v>207</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>252</v>
-      </c>
-      <c r="E6" s="27" t="s">
-        <v>251</v>
-      </c>
-      <c r="F6" t="s">
-        <v>265</v>
-      </c>
-      <c r="G6" t="s">
-        <v>215</v>
-      </c>
-      <c r="H6" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" t="s">
-        <v>220</v>
-      </c>
-      <c r="B7" t="s">
-        <v>221</v>
-      </c>
-      <c r="C7" t="s">
-        <v>207</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>250</v>
-      </c>
-      <c r="E7" s="27" t="s">
-        <v>251</v>
-      </c>
-      <c r="F7" t="s">
-        <v>212</v>
-      </c>
-      <c r="G7" t="s">
-        <v>215</v>
-      </c>
-      <c r="H7" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" t="s">
-        <v>257</v>
-      </c>
-      <c r="B8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C8" t="s">
-        <v>258</v>
-      </c>
-      <c r="D8">
-        <v>2013</v>
-      </c>
-      <c r="E8">
-        <v>2014</v>
-      </c>
-      <c r="F8" t="s">
-        <v>259</v>
-      </c>
-      <c r="G8" t="s">
-        <v>216</v>
-      </c>
-      <c r="H8" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" t="s">
-        <v>260</v>
-      </c>
-      <c r="B9" t="s">
-        <v>41</v>
-      </c>
-      <c r="C9" t="s">
-        <v>207</v>
-      </c>
-      <c r="D9">
-        <v>2014</v>
-      </c>
-      <c r="E9">
-        <v>2016</v>
-      </c>
-      <c r="F9" t="s">
-        <v>266</v>
-      </c>
-      <c r="G9" t="s">
-        <v>216</v>
-      </c>
-      <c r="H9" t="s">
-        <v>261</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/Data/ArthurHeimCareerDataEn.xlsx
+++ b/Data/ArthurHeimCareerDataEn.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arthurheim/Library/CloudStorage/Dropbox/Travail_encrypted_decrypted/PHD/career/Data_DrivenResume/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32CF7487-A669-FA40-8BD0-3C28C505BC92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{455CBB3B-12C5-4E4E-B056-CCBC8579AC85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8220" yWindow="500" windowWidth="27240" windowHeight="19200" xr2:uid="{65AA7443-0872-B84D-B38F-A133D7C4ED29}"/>
+    <workbookView xWindow="8220" yWindow="500" windowWidth="27240" windowHeight="19200" activeTab="10" xr2:uid="{65AA7443-0872-B84D-B38F-A133D7C4ED29}"/>
   </bookViews>
   <sheets>
     <sheet name="education" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="289">
   <si>
     <t>Degree</t>
   </si>
@@ -371,24 +371,15 @@
     <t>France Stratégie</t>
   </si>
   <si>
-    <t xml:space="preserve"> \emph{L'apport des évaluations des investissements sociaux dans la jeunesse}</t>
-  </si>
-  <si>
     <t>Paris</t>
   </si>
   <si>
     <t>LIEPP (Sciences Po)</t>
   </si>
   <si>
-    <t xml:space="preserve"> \it{École à 2 ans : Une maternelle plus précoce et plus longue améliore-t-elle la réussite des élèves ?}</t>
-  </si>
-  <si>
     <t xml:space="preserve"> OECD \&amp;  US institute for Education Sciences (IES)</t>
   </si>
   <si>
-    <t xml:space="preserve"> \emph{Quand la scolarisation à 2 ans n'apporte pas les effets attendus : Analyse quasi-expérimentales à partir du panel 2007}</t>
-  </si>
-  <si>
     <t>OECD</t>
   </si>
   <si>
@@ -396,15 +387,6 @@
   </si>
   <si>
     <t>Paris I Sorbonne</t>
-  </si>
-  <si>
-    <t>\emph{Rage against the matching}</t>
-  </si>
-  <si>
-    <t>\emph{Tax burden on the poor}</t>
-  </si>
-  <si>
-    <t>\emph{Welfare-to-What?}</t>
   </si>
   <si>
     <t>sep 2016</t>
@@ -755,9 +737,6 @@
   </si>
   <si>
     <t>GalitzineHeim2024</t>
-  </si>
-  <si>
-    <t>CarbucciaEtAl2024</t>
   </si>
   <si>
     <t>Rage against the matching:
@@ -803,25 +782,15 @@
     </r>
   </si>
   <si>
-    <t>Multi-arm RCT in the Paris region measuring the effects of providing information and administrative support to pregnant women to access formal childcare
-\\ \href{https://osf.io/rh7eb/?view_only=ef7409ac646544eaac946374de134892}{Pre-print and replication material: \faExternalLink}</t>
-  </si>
-  <si>
     <t>Intensive margin reactions and effects of family structure of a welfare-to-work programme for single parents consistent with heterogeneous incentives of the French tax-benefit system
 \\ \href{https://www.dropbox.com/scl/fi/xdhov425ez5n1jcxl053r/GalitzineHeim2024.pdf?rlkey=pdun971icjt4biq7ikwrm2ji1&amp;dl=0}{Draft: \faExternalLink} 
 \\ \href{https://www.dropbox.com/scl/fi/9dbpmcefmout7rwrwqvt6/TaxBurdenEnShort.pdf?rlkey=omrpuo36dge0phkd2havhxo5p&amp;dl=0}{Slides: \faExternalLink}</t>
   </si>
   <si>
-    <t>multi1002024</t>
-  </si>
-  <si>
     <t xml:space="preserve">\href{https://theses.fr/2024EHES0027}{Online access: \faExternalLink} 
 \\ \href{https://www.dropbox.com/scl/fi/7yl7ri3en9vak8h2nyt44/R-sum-AHeimPhDV2.pdf?rlkey=w9k81hwyt6eu6390tgd1mqa6u&amp;dl=0}{Summary in French: \faExternalLink} </t>
   </si>
   <si>
-    <t>Conducted replications of Angrist and Lavy (AER 2009) and Behrman et al. (JPE 2015) for the Multi 100 project, examining the impact of analyst choices on research outcomes.</t>
-  </si>
-  <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
@@ -922,15 +891,9 @@
     <t>OECD expert group |  ‘What standards of evidence are needed for policy design, implementation and evaluation’</t>
   </si>
   <si>
-    <t>\emph{Demand for international standards of evidence : thoughts from a French perspective}</t>
-  </si>
-  <si>
     <t>International conference | Using educational research and innovation to address inequality and achievement gaps in education</t>
   </si>
   <si>
-    <t xml:space="preserve"> \emph{Income support strategies to reduce inequalities : Insights from France}</t>
-  </si>
-  <si>
     <t>Conference | Social investment for the youths</t>
   </si>
   <si>
@@ -965,12 +928,6 @@
   </si>
   <si>
     <t>Nature Human Behaviour</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{\bf Forthcoming} </t>
-  </si>
-  <si>
-    <t>{\bf R \&amp; R} Nature Human Behaviour</t>
   </si>
   <si>
     <t>Working paper</t>
@@ -998,6 +955,28 @@
  \underline{PhD advisor:} \href{https://www.parisschoolofeconomics.eu/en/gurgand-marc/}{Marc Gurgand}  \\
  \underline{ Jury}:  \href{http://www.anneboring.com/}{Anne Boring}, \href{https://sites.google.com/site/rafaellalive/}{Rafael Lalive}, \href{https://sites.google.com/view/camilleterrier/accueil}{Camille Terrier}, \href{https://www.parisschoolofeconomics.eu/en/macours-karen/}{Karen Macours} \\
 \href{https://theses.fr/2024EHES0027}{Online access: \faExternalLink}  $\quad$ \href{https://www.dropbox.com/scl/fi/7yl7ri3en9vak8h2nyt44/R-sum-AHeimPhDV2.pdf?rlkey=w9k81hwyt6eu6390tgd1mqa6u&amp;dl=0}{Summary in French: \faExternalLink} </t>
+  </si>
+  <si>
+    <t>CarbucciaEtAl2025</t>
+  </si>
+  <si>
+    <t>Multi-arm RCT in the Paris region measuring the effects of providing information and administrative support to pregnant women to access formal childcare
+\\ \href{https://www.nature.com/articles/s41562-025-02293-4}{\faExternalLink}</t>
+  </si>
+  <si>
+    <t>multi1002025</t>
+  </si>
+  <si>
+    <t>Conducted replications for the Multi 100 project, examining the impact of analyst choices on research outcomes</t>
+  </si>
+  <si>
+    <t>Numérique en commun[s]</t>
+  </si>
+  <si>
+    <t>Oct 2025</t>
+  </si>
+  <si>
+    <t>Conférence | Numérique en commun[s] 2025</t>
   </si>
 </sst>
 </file>
@@ -1556,13 +1535,13 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="D2" t="s">
         <v>57</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>295</v>
+        <v>281</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="34">
@@ -1579,7 +1558,7 @@
         <v>56</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1626,7 +1605,7 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="4" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>14</v>
@@ -1647,174 +1626,174 @@
         <v>19</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="B2" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="C2" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="E2" s="26" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="F2" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="G2" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H2" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="B3" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="C3" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="E3" s="26" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="F3" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H3" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="B4" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="C4" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="E4" s="26" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="F4" t="s">
+        <v>199</v>
+      </c>
+      <c r="G4" t="s">
         <v>205</v>
       </c>
-      <c r="G4" t="s">
-        <v>211</v>
-      </c>
       <c r="H4" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="B5" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="C5" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="D5" s="12" t="s">
+        <v>229</v>
+      </c>
+      <c r="E5" s="26" t="s">
+        <v>236</v>
+      </c>
+      <c r="F5" t="s">
+        <v>200</v>
+      </c>
+      <c r="G5" t="s">
+        <v>204</v>
+      </c>
+      <c r="H5" t="s">
         <v>239</v>
-      </c>
-      <c r="E5" s="26" t="s">
-        <v>246</v>
-      </c>
-      <c r="F5" t="s">
-        <v>206</v>
-      </c>
-      <c r="G5" t="s">
-        <v>210</v>
-      </c>
-      <c r="H5" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="B6" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="C6" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="E6" s="26" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="F6" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="G6" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="H6" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="B7" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="C7" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="E7" s="26" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="F7" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G7" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="H7" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="B8" t="s">
         <v>39</v>
       </c>
       <c r="C8" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="D8">
         <v>2013</v>
@@ -1823,24 +1802,24 @@
         <v>2014</v>
       </c>
       <c r="F8" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="G8" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H8" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="B9" t="s">
         <v>39</v>
       </c>
       <c r="C9" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="D9">
         <v>2014</v>
@@ -1849,13 +1828,13 @@
         <v>2016</v>
       </c>
       <c r="F9" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="G9" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H9" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
     </row>
   </sheetData>
@@ -1865,9 +1844,10 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89004A4C-135E-AE46-AB58-A9B77E14C3A4}">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
+    <col min="1" max="1" width="28.83203125" customWidth="1"/>
     <col min="5" max="5" width="73.5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1893,81 +1873,71 @@
       <c r="G1" s="4"/>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" t="s">
-        <v>267</v>
-      </c>
-      <c r="B2" t="s">
-        <v>264</v>
-      </c>
-      <c r="C2" t="s">
-        <v>265</v>
-      </c>
-      <c r="D2" s="28" t="s">
-        <v>263</v>
-      </c>
-      <c r="E2" t="s">
-        <v>114</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="A2" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4" t="s">
         <v>21</v>
       </c>
       <c r="G2" s="4"/>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>190</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="D3" s="27" t="s">
-        <v>194</v>
-      </c>
-      <c r="E3" t="s">
-        <v>113</v>
-      </c>
-      <c r="F3" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="B3" t="s">
+        <v>254</v>
+      </c>
+      <c r="C3" t="s">
+        <v>255</v>
+      </c>
+      <c r="D3" s="28" t="s">
+        <v>253</v>
+      </c>
+      <c r="F3" t="s">
         <v>21</v>
       </c>
+      <c r="G3" s="4"/>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>130</v>
-      </c>
-      <c r="B4" t="s">
-        <v>129</v>
-      </c>
-      <c r="C4" t="s">
-        <v>104</v>
-      </c>
-      <c r="D4" s="26" t="s">
-        <v>266</v>
-      </c>
-      <c r="E4" t="s">
-        <v>112</v>
-      </c>
-      <c r="F4" t="s">
+        <v>184</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="D4" s="27" t="s">
+        <v>188</v>
+      </c>
+      <c r="F4" s="6" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="B5" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="C5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D5" s="26" t="s">
-        <v>121</v>
-      </c>
-      <c r="E5" t="s">
-        <v>113</v>
+        <v>256</v>
       </c>
       <c r="F5" t="s">
         <v>21</v>
@@ -1975,19 +1945,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>268</v>
+        <v>125</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>104</v>
       </c>
       <c r="C6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D6" s="26" t="s">
-        <v>120</v>
-      </c>
-      <c r="E6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F6" t="s">
         <v>21</v>
@@ -1995,18 +1962,15 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
       <c r="B7" t="s">
-        <v>111</v>
+        <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D7" s="26" t="s">
-        <v>119</v>
-      </c>
-      <c r="E7" t="s">
         <v>114</v>
       </c>
       <c r="F7" t="s">
@@ -2015,19 +1979,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="B8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D8" s="26" t="s">
-        <v>118</v>
-      </c>
-      <c r="E8" t="s">
-        <v>271</v>
+        <v>113</v>
       </c>
       <c r="F8" t="s">
         <v>21</v>
@@ -2035,19 +1996,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="B9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C9" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="D9" s="26" t="s">
-        <v>117</v>
-      </c>
-      <c r="E9" t="s">
-        <v>273</v>
+        <v>112</v>
       </c>
       <c r="F9" t="s">
         <v>21</v>
@@ -2055,19 +2013,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>276</v>
+        <v>261</v>
       </c>
       <c r="B10" t="s">
-        <v>277</v>
+        <v>105</v>
       </c>
       <c r="C10" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D10" s="26" t="s">
-        <v>117</v>
-      </c>
-      <c r="E10" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F10" t="s">
         <v>21</v>
@@ -2075,47 +2030,58 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="B11" t="s">
-        <v>105</v>
+        <v>265</v>
       </c>
       <c r="C11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D11" s="26" t="s">
-        <v>116</v>
-      </c>
-      <c r="E11" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="F11" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="B12" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C12" t="s">
-        <v>104</v>
-      </c>
-      <c r="D12" s="28" t="s">
-        <v>115</v>
-      </c>
-      <c r="E12" t="s">
         <v>103</v>
+      </c>
+      <c r="D12" s="26" t="s">
+        <v>110</v>
       </c>
       <c r="F12" t="s">
         <v>23</v>
       </c>
     </row>
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
+        <v>262</v>
+      </c>
+      <c r="B13" t="s">
+        <v>102</v>
+      </c>
+      <c r="C13" t="s">
+        <v>103</v>
+      </c>
+      <c r="D13" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="F13" t="s">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:F12">
-    <sortCondition descending="1" ref="D4:D12"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:F13">
+    <sortCondition descending="1" ref="D5:D13"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2151,23 +2117,23 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="17" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="B2" s="17" t="s">
         <v>75</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="E2" s="18" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="F2" s="17"/>
       <c r="G2" s="17" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -2187,7 +2153,7 @@
         <v>81</v>
       </c>
       <c r="G3" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -2207,7 +2173,7 @@
         <v>83</v>
       </c>
       <c r="G4" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -2227,7 +2193,7 @@
         <v>85</v>
       </c>
       <c r="G5" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -2280,19 +2246,19 @@
         <v>36</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>40</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>292</v>
+        <v>278</v>
       </c>
       <c r="G2" s="6" t="s">
         <v>21</v>
@@ -2306,7 +2272,7 @@
         <v>37</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>40</v>
@@ -2330,7 +2296,7 @@
         <v>38</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>40</v>
@@ -2354,7 +2320,7 @@
         <v>39</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>40</v>
@@ -2378,7 +2344,7 @@
         <v>39</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>40</v>
@@ -2444,22 +2410,22 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="D2" s="4">
         <v>2025</v>
       </c>
       <c r="E2" s="29" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="F2" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>21</v>
@@ -2470,22 +2436,22 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="C3" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="F3" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="G3" t="s">
         <v>21</v>
@@ -2496,22 +2462,22 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="B4" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="C4" t="s">
         <v>102</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="F4" t="s">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="G4" t="s">
         <v>21</v>
@@ -2522,22 +2488,22 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="B5" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="C5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="F5" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="G5" t="s">
         <v>21</v>
@@ -2548,22 +2514,22 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="B6" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="C6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="F6" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="G6" t="s">
         <v>21</v>
@@ -2612,90 +2578,90 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="B1" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="C1" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="B2" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="C2" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="B3" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="C3" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="B4" t="s">
+        <v>154</v>
+      </c>
+      <c r="C4" t="s">
         <v>160</v>
-      </c>
-      <c r="C4" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="B5" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="C5" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="B6" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="C6" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="B7" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="C7" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="B8" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="C8" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -2710,189 +2676,189 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="B1" s="9" t="s">
         <v>29</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="B2" t="s">
         <v>30</v>
       </c>
       <c r="C2" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="B3" t="s">
         <v>31</v>
       </c>
       <c r="C3" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="B4" t="s">
         <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="B5" t="s">
         <v>99</v>
       </c>
       <c r="C5" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="B6" t="s">
         <v>33</v>
       </c>
       <c r="C6" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="B7" t="s">
         <v>34</v>
       </c>
       <c r="C7" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="B8" t="s">
         <v>35</v>
       </c>
       <c r="C8" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="B9" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="C9" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B10" t="s">
         <v>98</v>
       </c>
       <c r="C10" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B11" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="C11" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B12" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="C12" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B13" t="s">
         <v>28</v>
       </c>
       <c r="C13" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B14" t="s">
         <v>96</v>
       </c>
       <c r="C14" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B15" t="s">
         <v>97</v>
       </c>
       <c r="C15" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="B16" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="C16" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="B17" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C17" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -2924,19 +2890,19 @@
     </row>
     <row r="2" spans="1:5" ht="119">
       <c r="A2" s="31" t="s">
-        <v>293</v>
+        <v>279</v>
       </c>
       <c r="B2" s="31">
         <v>2025</v>
       </c>
       <c r="C2" s="31" t="s">
-        <v>290</v>
+        <v>276</v>
       </c>
       <c r="D2" s="31" t="s">
-        <v>294</v>
+        <v>280</v>
       </c>
       <c r="E2" s="32" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3026,7 +2992,7 @@
         <v>21</v>
       </c>
       <c r="H2" s="16" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="24" customHeight="1">
@@ -3052,7 +3018,7 @@
         <v>21</v>
       </c>
       <c r="H3" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="24" customHeight="1">
@@ -3075,7 +3041,7 @@
         <v>21</v>
       </c>
       <c r="H4" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="24" customHeight="1">
@@ -3095,13 +3061,13 @@
         <v>2024</v>
       </c>
       <c r="F5" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="G5" t="s">
         <v>21</v>
       </c>
       <c r="H5" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="24" customHeight="1">
@@ -3115,7 +3081,7 @@
         <v>67</v>
       </c>
       <c r="D6" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="E6">
         <v>2024</v>
@@ -3175,19 +3141,19 @@
     </row>
     <row r="9" spans="1:8" ht="24" customHeight="1">
       <c r="B9" s="15" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C9" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="D9" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="E9">
         <v>2024</v>
       </c>
       <c r="F9" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="G9" t="s">
         <v>23</v>
@@ -3245,7 +3211,7 @@
       </c>
       <c r="C2" s="23"/>
       <c r="D2" s="23" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="E2" s="23">
         <v>2024</v>
@@ -3257,7 +3223,7 @@
         <v>21</v>
       </c>
       <c r="H2" s="24" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="85">
@@ -3277,13 +3243,13 @@
         <v>2024</v>
       </c>
       <c r="F3" s="23" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="G3" s="23" t="s">
         <v>21</v>
       </c>
       <c r="H3" s="23" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="119">
@@ -3307,7 +3273,7 @@
         <v>21</v>
       </c>
       <c r="H4" s="23" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="221">
@@ -3327,25 +3293,25 @@
         <v>2024</v>
       </c>
       <c r="F5" s="23" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="G5" s="23" t="s">
         <v>21</v>
       </c>
       <c r="H5" s="23" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="221">
       <c r="A6" s="23"/>
       <c r="B6" s="23" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="C6" s="23" t="s">
         <v>67</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="E6" s="23">
         <v>2024</v>
@@ -3409,19 +3375,19 @@
     <row r="9" spans="1:8" ht="153">
       <c r="A9" s="23"/>
       <c r="B9" s="25" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C9" s="23" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="D9" s="23" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="E9" s="23">
         <v>2024</v>
       </c>
       <c r="F9" s="23" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="G9" s="23" t="s">
         <v>21</v>
@@ -3443,7 +3409,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="17">
       <c r="A1" s="3" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="B1" s="20" t="s">
         <v>61</v>
@@ -3472,38 +3438,38 @@
     </row>
     <row r="2" spans="1:9" ht="136">
       <c r="A2" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="B2" s="23"/>
       <c r="C2" s="23" t="s">
         <v>51</v>
       </c>
       <c r="D2" s="23" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="E2" s="23" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="F2" s="23">
         <v>2024</v>
       </c>
       <c r="G2" s="23" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="H2" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I2" s="24" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="289">
       <c r="A3" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="B3" s="23"/>
       <c r="C3" s="23" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="D3" s="23" t="s">
         <v>44</v>
@@ -3515,51 +3481,51 @@
         <v>2024</v>
       </c>
       <c r="G3" s="23" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="H3" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I3" s="23" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="119">
       <c r="A4" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="B4" s="23" t="s">
         <v>60</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="E4" s="23" t="s">
-        <v>288</v>
+        <v>274</v>
       </c>
       <c r="F4" s="23">
         <v>2024</v>
       </c>
       <c r="G4" s="23" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="H4" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I4" s="23" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="306">
       <c r="A5" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="B5" s="23"/>
       <c r="C5" s="23" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="D5" s="23" t="s">
         <v>50</v>
@@ -3571,34 +3537,34 @@
         <v>2024</v>
       </c>
       <c r="G5" s="23" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="H5" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I5" s="23" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="170">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="153">
       <c r="A6" t="s">
-        <v>227</v>
+        <v>282</v>
       </c>
       <c r="B6" s="23"/>
       <c r="C6" s="23" t="s">
-        <v>289</v>
+        <v>275</v>
       </c>
       <c r="D6" s="23" t="s">
         <v>67</v>
       </c>
       <c r="E6" s="23" t="s">
-        <v>285</v>
-      </c>
-      <c r="F6" s="23" t="s">
-        <v>286</v>
+        <v>273</v>
+      </c>
+      <c r="F6" s="23">
+        <v>2025</v>
       </c>
       <c r="G6" s="23" t="s">
-        <v>233</v>
+        <v>283</v>
       </c>
       <c r="H6" s="23" t="s">
         <v>21</v>
@@ -3653,25 +3619,25 @@
       </c>
       <c r="I8" s="23"/>
     </row>
-    <row r="9" spans="1:9" ht="85">
+    <row r="9" spans="1:9" ht="68">
       <c r="A9" t="s">
-        <v>235</v>
+        <v>284</v>
       </c>
       <c r="B9" s="23"/>
       <c r="C9" s="25" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="D9" s="23" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="E9" s="23" t="s">
-        <v>287</v>
+        <v>273</v>
       </c>
       <c r="F9" s="23">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G9" s="23" t="s">
-        <v>237</v>
+        <v>285</v>
       </c>
       <c r="H9" s="23" t="s">
         <v>21</v>

--- a/Data/ArthurHeimCareerDataEn.xlsx
+++ b/Data/ArthurHeimCareerDataEn.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arthurheim/Library/CloudStorage/Dropbox/Travail_encrypted_decrypted/PHD/career/Data_DrivenResume/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{455CBB3B-12C5-4E4E-B056-CCBC8579AC85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{110C1282-D94F-8C45-B276-F82D24E2986A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8220" yWindow="500" windowWidth="27240" windowHeight="19200" activeTab="10" xr2:uid="{65AA7443-0872-B84D-B38F-A133D7C4ED29}"/>
+    <workbookView xWindow="8220" yWindow="500" windowWidth="27240" windowHeight="19200" activeTab="9" xr2:uid="{65AA7443-0872-B84D-B38F-A133D7C4ED29}"/>
   </bookViews>
   <sheets>
     <sheet name="education" sheetId="1" r:id="rId1"/>
@@ -694,9 +694,6 @@
     <t>Completed</t>
   </si>
   <si>
-    <t>POSAJE: Multi-arm RCT to foster access to formal early childcare</t>
-  </si>
-  <si>
     <t>ISAJE: Market design experiment of daycare assignments with random tie-breaks</t>
   </si>
   <si>
@@ -977,6 +974,9 @@
   </si>
   <si>
     <t>Conférence | Numérique en commun[s] 2025</t>
+  </si>
+  <si>
+    <t>Baby steps: Multi-arm RCT to foster access to formal early childcare</t>
   </si>
 </sst>
 </file>
@@ -1535,13 +1535,13 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D2" t="s">
         <v>57</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="34">
@@ -1626,7 +1626,7 @@
         <v>19</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1634,16 +1634,16 @@
         <v>203</v>
       </c>
       <c r="B2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C2" t="s">
         <v>193</v>
       </c>
       <c r="D2" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="E2" s="26" t="s">
         <v>233</v>
-      </c>
-      <c r="E2" s="26" t="s">
-        <v>234</v>
       </c>
       <c r="F2" t="s">
         <v>198</v>
@@ -1652,24 +1652,24 @@
         <v>205</v>
       </c>
       <c r="H2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>206</v>
+        <v>288</v>
       </c>
       <c r="B3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C3" t="s">
         <v>194</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E3" s="26" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F3" t="s">
         <v>197</v>
@@ -1678,24 +1678,24 @@
         <v>205</v>
       </c>
       <c r="H3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C4" t="s">
         <v>195</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E4" s="26" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F4" t="s">
         <v>199</v>
@@ -1704,24 +1704,24 @@
         <v>205</v>
       </c>
       <c r="H4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C5" t="s">
         <v>195</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E5" s="26" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F5" t="s">
         <v>200</v>
@@ -1730,50 +1730,50 @@
         <v>204</v>
       </c>
       <c r="H5" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C6" t="s">
         <v>196</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E6" s="26" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G6" t="s">
         <v>204</v>
       </c>
       <c r="H6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
+        <v>208</v>
+      </c>
+      <c r="B7" t="s">
         <v>209</v>
-      </c>
-      <c r="B7" t="s">
-        <v>210</v>
       </c>
       <c r="C7" t="s">
         <v>196</v>
       </c>
       <c r="D7" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="E7" s="26" t="s">
         <v>235</v>
-      </c>
-      <c r="E7" s="26" t="s">
-        <v>236</v>
       </c>
       <c r="F7" t="s">
         <v>201</v>
@@ -1782,18 +1782,18 @@
         <v>204</v>
       </c>
       <c r="H7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B8" t="s">
         <v>39</v>
       </c>
       <c r="C8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D8">
         <v>2013</v>
@@ -1802,18 +1802,18 @@
         <v>2014</v>
       </c>
       <c r="F8" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G8" t="s">
         <v>205</v>
       </c>
       <c r="H8" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B9" t="s">
         <v>39</v>
@@ -1828,13 +1828,13 @@
         <v>2016</v>
       </c>
       <c r="F9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G9" t="s">
         <v>205</v>
       </c>
       <c r="H9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
   </sheetData>
@@ -1874,16 +1874,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="D2" s="5" t="s">
         <v>286</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>287</v>
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="4" t="s">
@@ -1893,16 +1893,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C3" t="s">
         <v>254</v>
       </c>
-      <c r="C3" t="s">
-        <v>255</v>
-      </c>
       <c r="D3" s="28" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F3" t="s">
         <v>21</v>
@@ -1937,7 +1937,7 @@
         <v>103</v>
       </c>
       <c r="D5" s="26" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F5" t="s">
         <v>21</v>
@@ -1962,7 +1962,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B7" t="s">
         <v>5</v>
@@ -1979,7 +1979,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B8" t="s">
         <v>108</v>
@@ -1996,7 +1996,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B9" t="s">
         <v>106</v>
@@ -2013,7 +2013,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B10" t="s">
         <v>105</v>
@@ -2030,10 +2030,10 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
+        <v>263</v>
+      </c>
+      <c r="B11" t="s">
         <v>264</v>
-      </c>
-      <c r="B11" t="s">
-        <v>265</v>
       </c>
       <c r="C11" t="s">
         <v>103</v>
@@ -2047,7 +2047,7 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B12" t="s">
         <v>104</v>
@@ -2064,7 +2064,7 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B13" t="s">
         <v>102</v>
@@ -2153,7 +2153,7 @@
         <v>81</v>
       </c>
       <c r="G3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -2258,7 +2258,7 @@
         <v>20</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G2" s="6" t="s">
         <v>21</v>
@@ -2413,10 +2413,10 @@
         <v>180</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D2" s="4">
         <v>2025</v>
@@ -2425,7 +2425,7 @@
         <v>148</v>
       </c>
       <c r="F2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>21</v>
@@ -2445,13 +2445,13 @@
         <v>177</v>
       </c>
       <c r="D3" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="E3" s="12" t="s">
         <v>229</v>
       </c>
-      <c r="E3" s="12" t="s">
-        <v>230</v>
-      </c>
       <c r="F3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G3" t="s">
         <v>21</v>
@@ -2471,13 +2471,13 @@
         <v>102</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G4" t="s">
         <v>21</v>
@@ -2491,13 +2491,13 @@
         <v>180</v>
       </c>
       <c r="B5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C5" t="s">
         <v>103</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E5" s="13" t="s">
         <v>148</v>
@@ -2517,16 +2517,16 @@
         <v>180</v>
       </c>
       <c r="B6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C6" t="s">
         <v>103</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F6" t="s">
         <v>182</v>
@@ -2600,7 +2600,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B3" t="s">
         <v>154</v>
@@ -2633,13 +2633,13 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B6" t="s">
         <v>157</v>
       </c>
       <c r="C6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2890,19 +2890,19 @@
     </row>
     <row r="2" spans="1:5" ht="119">
       <c r="A2" s="31" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B2" s="31">
         <v>2025</v>
       </c>
       <c r="C2" s="31" t="s">
+        <v>275</v>
+      </c>
+      <c r="D2" s="31" t="s">
+        <v>279</v>
+      </c>
+      <c r="E2" s="32" t="s">
         <v>276</v>
-      </c>
-      <c r="D2" s="31" t="s">
-        <v>280</v>
-      </c>
-      <c r="E2" s="32" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3311,7 +3311,7 @@
         <v>67</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E6" s="23">
         <v>2024</v>
@@ -3381,7 +3381,7 @@
         <v>119</v>
       </c>
       <c r="D9" s="23" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E9" s="23">
         <v>2024</v>
@@ -3409,7 +3409,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="17">
       <c r="A1" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B1" s="20" t="s">
         <v>61</v>
@@ -3438,14 +3438,14 @@
     </row>
     <row r="2" spans="1:9" ht="136">
       <c r="A2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B2" s="23"/>
       <c r="C2" s="23" t="s">
         <v>51</v>
       </c>
       <c r="D2" s="23" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E2" s="23" t="s">
         <v>191</v>
@@ -3454,7 +3454,7 @@
         <v>2024</v>
       </c>
       <c r="G2" s="23" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H2" s="23" t="s">
         <v>21</v>
@@ -3465,11 +3465,11 @@
     </row>
     <row r="3" spans="1:9" ht="289">
       <c r="A3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B3" s="23"/>
       <c r="C3" s="23" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D3" s="23" t="s">
         <v>44</v>
@@ -3481,36 +3481,36 @@
         <v>2024</v>
       </c>
       <c r="G3" s="23" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H3" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I3" s="23" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="119">
       <c r="A4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B4" s="23" t="s">
         <v>60</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E4" s="23" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F4" s="23">
         <v>2024</v>
       </c>
       <c r="G4" s="23" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H4" s="23" t="s">
         <v>21</v>
@@ -3521,11 +3521,11 @@
     </row>
     <row r="5" spans="1:9" ht="306">
       <c r="A5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B5" s="23"/>
       <c r="C5" s="23" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D5" s="23" t="s">
         <v>50</v>
@@ -3537,7 +3537,7 @@
         <v>2024</v>
       </c>
       <c r="G5" s="23" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H5" s="23" t="s">
         <v>21</v>
@@ -3548,23 +3548,23 @@
     </row>
     <row r="6" spans="1:9" ht="153">
       <c r="A6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B6" s="23"/>
       <c r="C6" s="23" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D6" s="23" t="s">
         <v>67</v>
       </c>
       <c r="E6" s="23" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F6" s="23">
         <v>2025</v>
       </c>
       <c r="G6" s="23" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H6" s="23" t="s">
         <v>21</v>
@@ -3621,7 +3621,7 @@
     </row>
     <row r="9" spans="1:9" ht="68">
       <c r="A9" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B9" s="23"/>
       <c r="C9" s="25" t="s">
@@ -3631,13 +3631,13 @@
         <v>119</v>
       </c>
       <c r="E9" s="23" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F9" s="23">
         <v>2025</v>
       </c>
       <c r="G9" s="23" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H9" s="23" t="s">
         <v>21</v>
